--- a/automation_v1.xlsx
+++ b/automation_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1670" yWindow="-18110" windowWidth="27350" windowHeight="14430" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="serving_tuning" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -51,16 +51,17 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -109,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -143,10 +144,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -510,25 +510,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="8" customWidth="1" style="13" min="1" max="1"/>
-    <col width="52.7109375" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
-    <col width="20" bestFit="1" customWidth="1" style="13" min="3" max="4"/>
-    <col width="5" customWidth="1" style="13" min="5" max="6"/>
-    <col width="12" customWidth="1" style="13" min="7" max="7"/>
-    <col width="32" customWidth="1" style="13" min="8" max="8"/>
-    <col width="14" customWidth="1" style="13" min="9" max="10"/>
-    <col width="18" customWidth="1" style="13" min="11" max="11"/>
-    <col width="14" customWidth="1" style="13" min="12" max="12"/>
-    <col width="16" customWidth="1" style="13" min="13" max="13"/>
-    <col width="14" customWidth="1" style="13" min="14" max="15"/>
-    <col width="35" customWidth="1" style="13" min="16" max="16"/>
-    <col width="19" customWidth="1" style="13" min="17" max="18"/>
-    <col width="18" customWidth="1" style="13" min="19" max="21"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="52.7265625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20" bestFit="1" customWidth="1" min="3" max="4"/>
+    <col width="5" customWidth="1" min="5" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="15"/>
+    <col width="35" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="18"/>
+    <col width="18" customWidth="1" min="19" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="13">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>enabled</t>
@@ -631,8 +631,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="b">
-        <v>1</v>
+      <c r="A2" s="10" t="b">
+        <v>0</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
@@ -703,8 +703,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="b">
-        <v>1</v>
+      <c r="A3" s="10" t="b">
+        <v>0</v>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
@@ -775,8 +775,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="b">
-        <v>1</v>
+      <c r="A4" s="10" t="b">
+        <v>0</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
@@ -847,8 +847,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="b">
-        <v>1</v>
+      <c r="A5" s="10" t="b">
+        <v>0</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     </row>
     <row r="6">
       <c r="A6" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="8">
       <c r="A8" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="9">
       <c r="A9" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="10">
       <c r="A10" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="11">
       <c r="A11" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="12">
       <c r="A12" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="13">
       <c r="A13" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     </row>
     <row r="14">
       <c r="A14" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="15">
       <c r="A15" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="16">
       <c r="A16" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="17">
       <c r="A17" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="19">
       <c r="A19" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
     </row>
     <row r="21">
       <c r="A21" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="23">
       <c r="A23" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="25">
       <c r="A25" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="27">
       <c r="A27" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="29">
       <c r="A29" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="31">
       <c r="A31" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
     </row>
     <row r="33">
       <c r="A33" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="35">
       <c r="A35" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="37">
       <c r="A37" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="42">
       <c r="A42" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="47">
       <c r="A47" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="49">
       <c r="A49" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="51">
       <c r="A51" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="52">
       <c r="A52" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
     </row>
     <row r="53">
       <c r="A53" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="54">
       <c r="A54" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-14T14:50:26Z</t>
+          <t>2026-08-17T03:48:43Z</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-14T15:10:58Z</t>
+          <t>2026-08-17T04:01:40Z</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-14T15:17:12Z</t>
+          <t>2026-08-17T04:02:42Z</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4201,18 +4201,24 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-14T15:24:47Z</t>
+          <t>2026-08-17T19:40:24Z</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>3686</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>run_logs_dir=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-GPTQ-Int4/run_logs; wrapper_log=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-GPTQ-Int4/run_logs/Qwen--Qwen3-30B-A3B-GPTQ-Int4__in1024_out1024__bfloat16_cpu_tp2_dp2_wrapper.log; failure_context=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-GPTQ-Int4/run_logs/Qwen--Qwen3-30B-A3B-GPTQ-Int4__in1024_out1024__bfloat16_cpu_tp2_dp2_failure_context.log; server_failure_snapshot=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-GPTQ-Int4/run_logs/Qwen--Qwen3-30B-A3B-GPTQ-Int4__in1024_out1024__bfloat16_cpu_tp2_dp2_server_failure_snapshot.log</t>
-        </is>
+          <t>run_logs_dir=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-GPTQ-Int4/run_logs; recommendation=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-GPTQ-Int4/results/Qwen--Qwen3-30B-A3B-GPTQ-Int4__in1024_out1024__bfloat16_cpu_tp2_dp2_recommendation.txt; wrapper_log=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-GPTQ-Int4/run_logs/Qwen--Qwen3-30B-A3B-GPTQ-Int4__in1024_out1024__bfloat16_cpu_tp2_dp2_wrapper.log</t>
+        </is>
+      </c>
+      <c r="S58" t="n">
+        <v>4096</v>
       </c>
     </row>
     <row r="59">
@@ -4253,18 +4259,24 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-14T15:31:17Z</t>
+          <t>2026-08-18T05:59:51Z</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>3686</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>run_logs_dir=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/RedHatAI--Qwen3-30B-A3B-quantized.w4a16/run_logs; wrapper_log=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/RedHatAI--Qwen3-30B-A3B-quantized.w4a16/run_logs/RedHatAI--Qwen3-30B-A3B-quantized.w4a16__in1024_out1024__bfloat16_cpu_tp2_dp2_wrapper.log; failure_context=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/RedHatAI--Qwen3-30B-A3B-quantized.w4a16/run_logs/RedHatAI--Qwen3-30B-A3B-quantized.w4a16__in1024_out1024__bfloat16_cpu_tp2_dp2_failure_context.log; server_failure_snapshot=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/RedHatAI--Qwen3-30B-A3B-quantized.w4a16/run_logs/RedHatAI--Qwen3-30B-A3B-quantized.w4a16__in1024_out1024__bfloat16_cpu_tp2_dp2_server_failure_snapshot.log</t>
-        </is>
+          <t>run_logs_dir=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/RedHatAI--Qwen3-30B-A3B-quantized.w4a16/run_logs; recommendation=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/RedHatAI--Qwen3-30B-A3B-quantized.w4a16/results/RedHatAI--Qwen3-30B-A3B-quantized.w4a16__in1024_out1024__bfloat16_cpu_tp2_dp2_recommendation.txt; wrapper_log=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/RedHatAI--Qwen3-30B-A3B-quantized.w4a16/run_logs/RedHatAI--Qwen3-30B-A3B-quantized.w4a16__in1024_out1024__bfloat16_cpu_tp2_dp2_wrapper.log</t>
+        </is>
+      </c>
+      <c r="S59" t="n">
+        <v>4096</v>
       </c>
     </row>
     <row r="60">
@@ -4305,18 +4317,24 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-14T15:34:47Z</t>
+          <t>2026-08-18T21:04:23Z</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>3686</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>run_logs_dir=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8/run_logs; wrapper_log=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8/run_logs/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8__in1024_out1024__bfloat16_cpu_tp2_dp2_wrapper.log; failure_context=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8/run_logs/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8__in1024_out1024__bfloat16_cpu_tp2_dp2_failure_context.log; server_failure_snapshot=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8/run_logs/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8__in1024_out1024__bfloat16_cpu_tp2_dp2_server_failure_snapshot.log</t>
-        </is>
+          <t>run_logs_dir=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8/run_logs; recommendation=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8/results/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8__in1024_out1024__bfloat16_cpu_tp2_dp2_recommendation.txt; wrapper_log=/home/ubuntu/zepan/vLLM_benchmark/logs/get_c_regular/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8/run_logs/Qwen--Qwen3-30B-A3B-Instruct-2507-FP8__in1024_out1024__bfloat16_cpu_tp2_dp2_wrapper.log</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
+        <v>4096</v>
       </c>
     </row>
   </sheetData>
@@ -4331,14 +4349,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="28" customWidth="1" style="13" min="1" max="1"/>
-    <col width="10" customWidth="1" style="13" min="2" max="2"/>
-    <col width="70" customWidth="1" style="13" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Column</t>

--- a/automation_v1.xlsx
+++ b/automation_v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zepan\AppData\Roaming\MobaXterm\slash\mx86_64b\RemoteFiles\68860_18_6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zepan\AppData\Roaming\MobaXterm\slash\mx86_64b\RemoteFiles\264784_13_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B162A1-4F6D-44F4-A7C1-D70BF3CB625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08365568-A4F8-44D6-935D-36DC3A36AC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1130" yWindow="-16820" windowWidth="29860" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5840" yWindow="-18550" windowWidth="20800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="serving_tuning" sheetId="1" r:id="rId1"/>
@@ -1142,7 +1142,7 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="52.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
     <col min="5" max="6" width="5" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
@@ -1258,13 +1258,13 @@
         <v>1373</v>
       </c>
       <c r="O2" s="5">
-        <v>377.48</v>
+        <v>2516.16</v>
       </c>
       <c r="P2" s="7">
-        <v>4638</v>
+        <v>78556.460000000006</v>
       </c>
       <c r="Q2" s="7">
-        <v>86.68</v>
+        <v>510.65</v>
       </c>
       <c r="R2" s="7" t="s">
         <v>26</v>
@@ -1316,13 +1316,13 @@
         <v>5719</v>
       </c>
       <c r="O3" s="5">
-        <v>7525.75</v>
+        <v>12425.72</v>
       </c>
       <c r="P3" s="7">
-        <v>3589</v>
+        <v>50580.94</v>
       </c>
       <c r="Q3" s="7">
-        <v>42.82</v>
+        <v>446.5</v>
       </c>
       <c r="R3" s="7" t="s">
         <v>29</v>
@@ -1374,13 +1374,13 @@
         <v>1613</v>
       </c>
       <c r="O4" s="5">
-        <v>880.39</v>
+        <v>4131.16</v>
       </c>
       <c r="P4" s="7">
-        <v>3522</v>
+        <v>38044.54</v>
       </c>
       <c r="Q4" s="7">
-        <v>99.86</v>
+        <v>388.81</v>
       </c>
       <c r="R4" s="7" t="s">
         <v>32</v>
@@ -1432,13 +1432,13 @@
         <v>1843</v>
       </c>
       <c r="O5" s="8">
-        <v>5.87</v>
+        <v>289.69</v>
       </c>
       <c r="P5" s="8">
-        <v>1790</v>
+        <v>1518164.97</v>
       </c>
       <c r="Q5" s="8">
-        <v>168.67</v>
+        <v>5498.04</v>
       </c>
       <c r="R5" s="8" t="s">
         <v>36</v>
@@ -1489,13 +1489,13 @@
         <v>3293</v>
       </c>
       <c r="O6" s="10">
-        <v>29.64</v>
+        <v>769.77</v>
       </c>
       <c r="P6" s="10">
-        <v>1581</v>
+        <v>865791.86</v>
       </c>
       <c r="Q6" s="10">
-        <v>99.74</v>
+        <v>3750.37</v>
       </c>
       <c r="R6" s="10" t="s">
         <v>40</v>
@@ -1544,13 +1544,13 @@
         <v>921</v>
       </c>
       <c r="O7" s="10">
-        <v>41.42</v>
+        <v>791.28</v>
       </c>
       <c r="P7" s="10">
-        <v>2612</v>
+        <v>217520.79</v>
       </c>
       <c r="Q7" s="10">
-        <v>94.1</v>
+        <v>1070.5</v>
       </c>
       <c r="R7" s="10" t="s">
         <v>44</v>
@@ -1704,13 +1704,13 @@
         <v>1228</v>
       </c>
       <c r="O10" s="10">
-        <v>6667.22</v>
+        <v>8613.93</v>
       </c>
       <c r="P10" s="10">
-        <v>2322</v>
+        <v>5925.43</v>
       </c>
       <c r="Q10" s="10">
-        <v>66.61</v>
+        <v>146.72</v>
       </c>
       <c r="R10" s="10" t="s">
         <v>54</v>
@@ -1759,13 +1759,13 @@
         <v>3686</v>
       </c>
       <c r="O11" s="10">
-        <v>1779.28</v>
+        <v>4205.91</v>
       </c>
       <c r="P11" s="10">
-        <v>4991</v>
+        <v>97193.14</v>
       </c>
       <c r="Q11" s="10">
-        <v>72.86</v>
+        <v>858.9</v>
       </c>
       <c r="R11" s="10" t="s">
         <v>57</v>
@@ -1814,13 +1814,13 @@
         <v>921</v>
       </c>
       <c r="O12" s="10">
-        <v>261.55</v>
+        <v>953.87</v>
       </c>
       <c r="P12" s="10">
-        <v>4883</v>
+        <v>124495.52</v>
       </c>
       <c r="Q12" s="10">
-        <v>89.22</v>
+        <v>939.57</v>
       </c>
       <c r="R12" s="10" t="s">
         <v>60</v>
@@ -1869,13 +1869,13 @@
         <v>388</v>
       </c>
       <c r="O13" s="10">
-        <v>198.46</v>
+        <v>1094.58</v>
       </c>
       <c r="P13" s="10">
-        <v>2017</v>
+        <v>31821.8</v>
       </c>
       <c r="Q13" s="10">
-        <v>99.88</v>
+        <v>358.99</v>
       </c>
       <c r="R13" s="10" t="s">
         <v>63</v>
@@ -1959,6 +1959,15 @@
       <c r="N15">
         <v>7372</v>
       </c>
+      <c r="O15">
+        <v>4875.7700000000004</v>
+      </c>
+      <c r="P15">
+        <v>236767.78</v>
+      </c>
+      <c r="Q15">
+        <v>1385.41</v>
+      </c>
       <c r="R15" t="s">
         <v>69</v>
       </c>
@@ -2002,6 +2011,15 @@
       </c>
       <c r="N16">
         <v>921</v>
+      </c>
+      <c r="O16">
+        <v>676.78</v>
+      </c>
+      <c r="P16">
+        <v>179782.36</v>
+      </c>
+      <c r="Q16">
+        <v>1313.13</v>
       </c>
       <c r="R16" t="s">
         <v>72</v>
@@ -2050,13 +2068,13 @@
         <v>1201</v>
       </c>
       <c r="O17" s="10">
-        <v>208.03</v>
+        <v>1063.56</v>
       </c>
       <c r="P17" s="10">
-        <v>4800</v>
+        <v>175099.15</v>
       </c>
       <c r="Q17" s="10">
-        <v>86.68</v>
+        <v>1069.92</v>
       </c>
       <c r="R17" s="10" t="s">
         <v>75</v>
@@ -2105,13 +2123,13 @@
         <v>1353</v>
       </c>
       <c r="O18" s="10">
-        <v>614.35</v>
+        <v>3485.5</v>
       </c>
       <c r="P18" s="10">
-        <v>2713</v>
+        <v>36736.89</v>
       </c>
       <c r="Q18" s="10">
-        <v>99.59</v>
+        <v>387.03</v>
       </c>
       <c r="R18" s="10" t="s">
         <v>78</v>
@@ -2160,13 +2178,13 @@
         <v>1843</v>
       </c>
       <c r="O19" s="10">
-        <v>106.38</v>
+        <v>1200.7</v>
       </c>
       <c r="P19" s="10">
-        <v>2595</v>
+        <v>268958.63</v>
       </c>
       <c r="Q19" s="10">
-        <v>97.88</v>
+        <v>1417.92</v>
       </c>
       <c r="R19" s="10" t="s">
         <v>81</v>
@@ -2215,13 +2233,13 @@
         <v>3556</v>
       </c>
       <c r="O20" s="10">
-        <v>478.07</v>
+        <v>2585.46</v>
       </c>
       <c r="P20" s="10">
-        <v>4004</v>
+        <v>192789.27</v>
       </c>
       <c r="Q20" s="10">
-        <v>98.58</v>
+        <v>1308.6199999999999</v>
       </c>
       <c r="R20" s="10" t="s">
         <v>84</v>
@@ -2272,13 +2290,13 @@
         <v>2781</v>
       </c>
       <c r="O21" s="10">
-        <v>170.07</v>
+        <v>2152.2800000000002</v>
       </c>
       <c r="P21" s="10">
-        <v>2428</v>
+        <v>207682.79</v>
       </c>
       <c r="Q21" s="10">
-        <v>99.6</v>
+        <v>1206.04</v>
       </c>
       <c r="R21" s="10" t="s">
         <v>88</v>
@@ -2327,13 +2345,13 @@
         <v>1630</v>
       </c>
       <c r="O22" s="10">
-        <v>3530.17</v>
+        <v>5024.53</v>
       </c>
       <c r="P22" s="10">
-        <v>4957</v>
+        <v>20992.05</v>
       </c>
       <c r="Q22" s="10">
-        <v>85.89</v>
+        <v>335.07</v>
       </c>
       <c r="R22" s="10" t="s">
         <v>91</v>
@@ -2382,13 +2400,13 @@
         <v>1031</v>
       </c>
       <c r="O23" s="10">
-        <v>1213.6099999999999</v>
+        <v>3239.79</v>
       </c>
       <c r="P23" s="10">
-        <v>4760</v>
+        <v>31054.94</v>
       </c>
       <c r="Q23" s="10">
-        <v>76.31</v>
+        <v>317.02999999999997</v>
       </c>
       <c r="R23" s="10" t="s">
         <v>94</v>
@@ -2437,13 +2455,13 @@
         <v>1220</v>
       </c>
       <c r="O24" s="10">
-        <v>421.16</v>
+        <v>2358.87</v>
       </c>
       <c r="P24" s="10">
-        <v>4831</v>
+        <v>69665.52</v>
       </c>
       <c r="Q24" s="10">
-        <v>89.52</v>
+        <v>488.6</v>
       </c>
       <c r="R24" s="10" t="s">
         <v>97</v>
@@ -2492,13 +2510,13 @@
         <v>2906</v>
       </c>
       <c r="O25" s="10">
-        <v>478.82</v>
+        <v>3709.52</v>
       </c>
       <c r="P25" s="10">
-        <v>3461</v>
+        <v>137152.88</v>
       </c>
       <c r="Q25" s="10">
-        <v>99.6</v>
+        <v>709.54</v>
       </c>
       <c r="R25" s="10" t="s">
         <v>100</v>
@@ -2547,13 +2565,13 @@
         <v>1384</v>
       </c>
       <c r="O26" s="10">
-        <v>390.16</v>
+        <v>2601.9899999999998</v>
       </c>
       <c r="P26" s="10">
-        <v>4681</v>
+        <v>77724.5</v>
       </c>
       <c r="Q26" s="10">
-        <v>80.3</v>
+        <v>499.26</v>
       </c>
       <c r="R26" s="10" t="s">
         <v>103</v>
@@ -2602,13 +2620,13 @@
         <v>2276</v>
       </c>
       <c r="O27" s="10">
-        <v>2482.15</v>
+        <v>5265.59</v>
       </c>
       <c r="P27" s="10">
-        <v>4950</v>
+        <v>47176.29</v>
       </c>
       <c r="Q27" s="10">
-        <v>63.97</v>
+        <v>428.66</v>
       </c>
       <c r="R27" s="10" t="s">
         <v>106</v>
@@ -2657,13 +2675,13 @@
         <v>3686</v>
       </c>
       <c r="O28" s="10">
-        <v>301.70999999999998</v>
+        <v>3089</v>
       </c>
       <c r="P28" s="10">
-        <v>4813</v>
+        <v>227187.26</v>
       </c>
       <c r="Q28" s="10">
-        <v>95.36</v>
+        <v>1005.27</v>
       </c>
       <c r="R28" s="10" t="s">
         <v>109</v>
@@ -2862,13 +2880,13 @@
         <v>1388</v>
       </c>
       <c r="O32" s="10">
-        <v>916.51</v>
+        <v>3298.73</v>
       </c>
       <c r="P32" s="10">
-        <v>4991</v>
+        <v>48893.42</v>
       </c>
       <c r="Q32" s="10">
-        <v>63.18</v>
+        <v>412.84</v>
       </c>
       <c r="R32" s="10" t="s">
         <v>122</v>
@@ -2917,13 +2935,13 @@
         <v>5718</v>
       </c>
       <c r="O33" s="10">
-        <v>8207.82</v>
+        <v>13783.87</v>
       </c>
       <c r="P33" s="10">
-        <v>3236</v>
+        <v>42861.02</v>
       </c>
       <c r="Q33" s="10">
-        <v>39.25</v>
+        <v>403.57</v>
       </c>
       <c r="R33" s="10" t="s">
         <v>125</v>
@@ -2972,13 +2990,13 @@
         <v>1620</v>
       </c>
       <c r="O34" s="10">
-        <v>1118.08</v>
+        <v>4871.22</v>
       </c>
       <c r="P34" s="10">
-        <v>3250</v>
+        <v>26428.85</v>
       </c>
       <c r="Q34" s="10">
-        <v>97.82</v>
+        <v>340.46</v>
       </c>
       <c r="R34" s="10" t="s">
         <v>128</v>
@@ -3027,13 +3045,13 @@
         <v>613</v>
       </c>
       <c r="O35" s="10">
-        <v>5.68</v>
+        <v>437.22</v>
       </c>
       <c r="P35" s="10">
-        <v>2855</v>
+        <v>276257.21000000002</v>
       </c>
       <c r="Q35" s="10">
-        <v>173.51</v>
+        <v>1286.8900000000001</v>
       </c>
       <c r="R35" s="10" t="s">
         <v>131</v>
@@ -3082,13 +3100,13 @@
         <v>921</v>
       </c>
       <c r="O36" s="10">
-        <v>21.6</v>
+        <v>792.45</v>
       </c>
       <c r="P36" s="10">
-        <v>1037</v>
+        <v>201585.59</v>
       </c>
       <c r="Q36" s="10">
-        <v>90.69</v>
+        <v>1090.3699999999999</v>
       </c>
       <c r="R36" s="10" t="s">
         <v>134</v>
@@ -3137,13 +3155,13 @@
         <v>1390</v>
       </c>
       <c r="O37" s="10">
-        <v>904.69</v>
+        <v>3316.48</v>
       </c>
       <c r="P37" s="10">
-        <v>4718</v>
+        <v>47926.23</v>
       </c>
       <c r="Q37" s="10">
-        <v>63.11</v>
+        <v>415.09</v>
       </c>
       <c r="R37" s="10" t="s">
         <v>137</v>
@@ -3305,6 +3323,15 @@
       <c r="N42">
         <v>1095</v>
       </c>
+      <c r="O42">
+        <v>1209.3</v>
+      </c>
+      <c r="P42">
+        <v>188321.33</v>
+      </c>
+      <c r="Q42">
+        <v>799.05</v>
+      </c>
       <c r="R42" t="s">
         <v>146</v>
       </c>
@@ -3439,13 +3466,13 @@
         <v>1208</v>
       </c>
       <c r="O46" s="10">
-        <v>575.97</v>
+        <v>2494.27</v>
       </c>
       <c r="P46" s="10">
-        <v>4899</v>
+        <v>66621.960000000006</v>
       </c>
       <c r="Q46" s="10">
-        <v>93.03</v>
+        <v>447.34</v>
       </c>
       <c r="R46" s="10" t="s">
         <v>152</v>
@@ -3494,13 +3521,13 @@
         <v>3686</v>
       </c>
       <c r="O47" s="10">
-        <v>7191.72</v>
+        <v>11673.59</v>
       </c>
       <c r="P47" s="10">
-        <v>4941</v>
+        <v>37021.410000000003</v>
       </c>
       <c r="Q47" s="10">
-        <v>41.26</v>
+        <v>300.83</v>
       </c>
       <c r="R47" s="10" t="s">
         <v>155</v>
@@ -3601,13 +3628,13 @@
         <v>115</v>
       </c>
       <c r="O49" s="10">
-        <v>7.18</v>
+        <v>74.87</v>
       </c>
       <c r="P49" s="10">
-        <v>1523</v>
+        <v>478345.52</v>
       </c>
       <c r="Q49" s="10">
-        <v>137.84</v>
+        <v>1242.56</v>
       </c>
       <c r="R49" s="10" t="s">
         <v>161</v>
@@ -3656,13 +3683,13 @@
         <v>921</v>
       </c>
       <c r="O50" s="10">
-        <v>135.68</v>
+        <v>1178.8900000000001</v>
       </c>
       <c r="P50" s="10">
-        <v>3912</v>
+        <v>145922.29</v>
       </c>
       <c r="Q50" s="10">
-        <v>99.01</v>
+        <v>721.11</v>
       </c>
       <c r="R50" s="10" t="s">
         <v>164</v>
@@ -3711,13 +3738,13 @@
         <v>1253</v>
       </c>
       <c r="O51" s="10">
-        <v>581.11</v>
+        <v>2608.27</v>
       </c>
       <c r="P51" s="10">
-        <v>4765</v>
+        <v>72707.75</v>
       </c>
       <c r="Q51" s="10">
-        <v>86.92</v>
+        <v>444.31</v>
       </c>
       <c r="R51" s="10" t="s">
         <v>167</v>
@@ -3766,13 +3793,13 @@
         <v>1922</v>
       </c>
       <c r="O52" s="10">
-        <v>5346.7</v>
+        <v>7028.05</v>
       </c>
       <c r="P52" s="10">
-        <v>2752</v>
+        <v>9750.0300000000007</v>
       </c>
       <c r="Q52" s="10">
-        <v>64.84</v>
+        <v>287.68</v>
       </c>
       <c r="R52" s="10" t="s">
         <v>170</v>
@@ -3821,13 +3848,13 @@
         <v>4577</v>
       </c>
       <c r="O53" s="10">
-        <v>7436.79</v>
+        <v>14624.43</v>
       </c>
       <c r="P53" s="10">
-        <v>4953</v>
+        <v>44989.88</v>
       </c>
       <c r="Q53" s="10">
-        <v>35.700000000000003</v>
+        <v>284.5</v>
       </c>
       <c r="R53" s="10" t="s">
         <v>173</v>
@@ -3876,13 +3903,13 @@
         <v>8370</v>
       </c>
       <c r="O54" s="10">
-        <v>7213.04</v>
+        <v>12916.39</v>
       </c>
       <c r="P54" s="10">
-        <v>4983</v>
+        <v>112404.25</v>
       </c>
       <c r="Q54" s="10">
-        <v>37.299999999999997</v>
+        <v>589.39</v>
       </c>
       <c r="R54" s="10" t="s">
         <v>176</v>
@@ -4042,6 +4069,15 @@
       <c r="N58">
         <v>3686</v>
       </c>
+      <c r="O58">
+        <v>2535.61</v>
+      </c>
+      <c r="P58">
+        <v>214934.29</v>
+      </c>
+      <c r="Q58">
+        <v>1358.33</v>
+      </c>
       <c r="R58" t="s">
         <v>188</v>
       </c>
@@ -4086,6 +4122,15 @@
       <c r="N59">
         <v>3686</v>
       </c>
+      <c r="O59">
+        <v>2507.16</v>
+      </c>
+      <c r="P59">
+        <v>219170.21</v>
+      </c>
+      <c r="Q59">
+        <v>1365.26</v>
+      </c>
       <c r="R59" t="s">
         <v>191</v>
       </c>
@@ -4129,6 +4174,15 @@
       </c>
       <c r="N60">
         <v>3686</v>
+      </c>
+      <c r="O60">
+        <v>2481.15</v>
+      </c>
+      <c r="P60">
+        <v>209543.62</v>
+      </c>
+      <c r="Q60">
+        <v>1409.38</v>
       </c>
       <c r="R60" t="s">
         <v>194</v>
